--- a/AAII_Financials/Quarterly/AWH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AWH_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>AWH</t>
   </si>
@@ -656,171 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="E8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F8" s="3">
         <v>2300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>2100</v>
       </c>
       <c r="H8" s="3">
         <v>2100</v>
       </c>
       <c r="I8" s="3">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="J8" s="3">
         <v>1900</v>
       </c>
       <c r="K8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L8" s="3">
         <v>1700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1200</v>
-      </c>
-      <c r="R8" s="3">
-        <v>1300</v>
       </c>
       <c r="S8" s="3">
         <v>1300</v>
       </c>
       <c r="T8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U8" s="3">
         <v>1100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -828,129 +835,135 @@
         <v>900</v>
       </c>
       <c r="E9" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F9" s="3">
         <v>1100</v>
-      </c>
-      <c r="F9" s="3">
-        <v>900</v>
       </c>
       <c r="G9" s="3">
         <v>900</v>
       </c>
       <c r="H9" s="3">
+        <v>900</v>
+      </c>
+      <c r="I9" s="3">
         <v>1100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>600</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>800</v>
       </c>
       <c r="R9" s="3">
         <v>800</v>
       </c>
       <c r="S9" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="T9" s="3">
         <v>900</v>
       </c>
       <c r="U9" s="3">
+        <v>900</v>
+      </c>
+      <c r="V9" s="3">
         <v>700</v>
-      </c>
-      <c r="V9" s="3">
-        <v>800</v>
       </c>
       <c r="W9" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="E10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F10" s="3">
         <v>1200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1000</v>
       </c>
       <c r="I10" s="3">
         <v>1000</v>
       </c>
       <c r="J10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K10" s="3">
         <v>1100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>200</v>
-      </c>
-      <c r="U10" s="3">
-        <v>100</v>
       </c>
       <c r="V10" s="3">
         <v>100</v>
       </c>
       <c r="W10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="X10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,31 +987,32 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="E12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F12" s="3">
         <v>1200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1300</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1500</v>
       </c>
       <c r="K12" s="3">
         <v>1500</v>
@@ -1007,40 +1021,43 @@
         <v>1500</v>
       </c>
       <c r="M12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N12" s="3">
         <v>900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>600</v>
-      </c>
-      <c r="P12" s="3">
-        <v>400</v>
       </c>
       <c r="Q12" s="3">
         <v>400</v>
       </c>
       <c r="R12" s="3">
+        <v>400</v>
+      </c>
+      <c r="S12" s="3">
         <v>200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>300</v>
-      </c>
-      <c r="T12" s="3">
-        <v>200</v>
       </c>
       <c r="U12" s="3">
         <v>200</v>
       </c>
       <c r="V12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W12" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1104,8 +1121,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1115,11 +1135,11 @@
       <c r="E14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>55</v>
@@ -1136,8 +1156,8 @@
       <c r="L14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1169,8 +1189,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>6800</v>
+        <v>6300</v>
       </c>
       <c r="E17" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F17" s="3">
         <v>8100</v>
       </c>
-      <c r="F17" s="3">
-        <v>7800</v>
-      </c>
       <c r="G17" s="3">
-        <v>11800</v>
+        <v>7200</v>
       </c>
       <c r="H17" s="3">
+        <v>10700</v>
+      </c>
+      <c r="I17" s="3">
         <v>10300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="P18" s="3">
         <v>-4300</v>
       </c>
-      <c r="E18" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-9200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-8100</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="S18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="T18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="U18" s="3">
         <v>-4300</v>
       </c>
-      <c r="P18" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1411,41 +1444,42 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>2000</v>
+        <v>-600</v>
       </c>
       <c r="E20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
-        <v>5100</v>
-      </c>
       <c r="H20" s="3">
+        <v>800</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>-100</v>
       </c>
       <c r="L20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1456,11 +1490,11 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1476,73 +1510,79 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-2300</v>
+        <v>-4700</v>
       </c>
       <c r="E21" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-6000</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-5000</v>
       </c>
       <c r="G21" s="3">
         <v>-4500</v>
       </c>
       <c r="H21" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-8200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-9600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1606,73 +1646,79 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>-2300</v>
+        <v>-4700</v>
       </c>
       <c r="E23" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-6100</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-5100</v>
       </c>
       <c r="G23" s="3">
         <v>-4600</v>
       </c>
       <c r="H23" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="I23" s="3">
         <v>-8200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1736,8 +1782,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-2300</v>
+        <v>-4700</v>
       </c>
       <c r="E26" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-6100</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-5100</v>
       </c>
       <c r="G26" s="3">
         <v>-4600</v>
       </c>
       <c r="H26" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="I26" s="3">
         <v>-8200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-2300</v>
+        <v>-4700</v>
       </c>
       <c r="E27" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-6100</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-5100</v>
       </c>
       <c r="G27" s="3">
         <v>-4600</v>
       </c>
       <c r="H27" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="I27" s="3">
         <v>-8200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,41 +2258,44 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-2000</v>
+        <v>600</v>
       </c>
       <c r="E32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
-        <v>-5100</v>
-      </c>
       <c r="H32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>100</v>
       </c>
       <c r="L32" s="3">
+        <v>100</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2236,11 +2306,11 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2256,73 +2326,79 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>-2300</v>
+        <v>-4700</v>
       </c>
       <c r="E33" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-6100</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-5100</v>
       </c>
       <c r="G33" s="3">
         <v>-4600</v>
       </c>
       <c r="H33" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="I33" s="3">
         <v>-8200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>-2300</v>
+        <v>-4700</v>
       </c>
       <c r="E35" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-6100</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-5100</v>
       </c>
       <c r="G35" s="3">
         <v>-4600</v>
       </c>
       <c r="H35" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="I35" s="3">
         <v>-8200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2571,73 +2657,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E41" s="3">
         <v>4200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>26900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>37200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>44900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>53000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>59400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>18800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>14600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2701,8 +2791,11 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
@@ -2713,61 +2806,64 @@
         <v>1600</v>
       </c>
       <c r="F43" s="3">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="G43" s="3">
         <v>1200</v>
       </c>
       <c r="H43" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="I43" s="3">
         <v>1100</v>
       </c>
       <c r="J43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K43" s="3">
         <v>1000</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1100</v>
       </c>
       <c r="L43" s="3">
         <v>1100</v>
       </c>
       <c r="M43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N43" s="3">
         <v>1000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>900</v>
-      </c>
-      <c r="O43" s="3">
-        <v>800</v>
       </c>
       <c r="P43" s="3">
         <v>800</v>
       </c>
       <c r="Q43" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="R43" s="3">
         <v>900</v>
       </c>
       <c r="S43" s="3">
+        <v>900</v>
+      </c>
+      <c r="T43" s="3">
         <v>1000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
@@ -2784,7 +2880,7 @@
         <v>300</v>
       </c>
       <c r="H44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I44" s="3">
         <v>200</v>
@@ -2793,7 +2889,7 @@
         <v>200</v>
       </c>
       <c r="K44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L44" s="3">
         <v>100</v>
@@ -2802,25 +2898,25 @@
         <v>100</v>
       </c>
       <c r="N44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
       </c>
       <c r="P44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3">
         <v>100</v>
       </c>
       <c r="R44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
       </c>
       <c r="T44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U44" s="3">
         <v>100</v>
@@ -2831,138 +2927,147 @@
       <c r="W44" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3">
         <v>700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1600</v>
       </c>
       <c r="J45" s="3">
         <v>1600</v>
       </c>
       <c r="K45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L45" s="3">
         <v>1100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>900</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>800</v>
       </c>
       <c r="R45" s="3">
         <v>800</v>
       </c>
       <c r="S45" s="3">
+        <v>800</v>
+      </c>
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>500</v>
-      </c>
-      <c r="U45" s="3">
-        <v>600</v>
       </c>
       <c r="V45" s="3">
         <v>600</v>
       </c>
       <c r="W45" s="3">
+        <v>600</v>
+      </c>
+      <c r="X45" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E46" s="3">
         <v>6900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16300</v>
-      </c>
-      <c r="G46" s="3">
-        <v>23000</v>
       </c>
       <c r="H46" s="3">
         <v>23000</v>
       </c>
       <c r="I46" s="3">
+        <v>23000</v>
+      </c>
+      <c r="J46" s="3">
         <v>29800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>40000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>47200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>54900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>61400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>13400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>16100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>17600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -3026,25 +3131,28 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E48" s="3">
         <v>600</v>
       </c>
       <c r="F48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G48" s="3">
         <v>700</v>
       </c>
       <c r="H48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="I48" s="3">
         <v>800</v>
@@ -3053,7 +3161,7 @@
         <v>800</v>
       </c>
       <c r="K48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="L48" s="3">
         <v>900</v>
@@ -3062,37 +3170,40 @@
         <v>900</v>
       </c>
       <c r="N48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="O48" s="3">
         <v>1000</v>
       </c>
       <c r="P48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q48" s="3">
         <v>400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>300</v>
-      </c>
-      <c r="R48" s="3">
-        <v>400</v>
       </c>
       <c r="S48" s="3">
         <v>400</v>
       </c>
       <c r="T48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="U48" s="3">
         <v>500</v>
       </c>
       <c r="V48" s="3">
+        <v>500</v>
+      </c>
+      <c r="W48" s="3">
         <v>600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -3286,8 +3403,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
@@ -3295,13 +3415,13 @@
         <v>300</v>
       </c>
       <c r="E52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F52" s="3">
         <v>400</v>
       </c>
       <c r="G52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H52" s="3">
         <v>300</v>
@@ -3313,7 +3433,7 @@
         <v>300</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -3334,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="R52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S52" s="3">
         <v>100</v>
@@ -3346,13 +3466,16 @@
         <v>100</v>
       </c>
       <c r="V52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -3416,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E54" s="3">
         <v>7700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>24000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>30900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>41100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>48000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>55800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>62300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>18200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>11400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -3531,117 +3661,121 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
-      </c>
-      <c r="E57" s="3">
-        <v>900</v>
       </c>
       <c r="F57" s="3">
         <v>900</v>
       </c>
       <c r="G57" s="3">
+        <v>900</v>
+      </c>
+      <c r="H57" s="3">
         <v>1900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
         <v>600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>600</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>200</v>
       </c>
       <c r="R58" s="3">
         <v>200</v>
@@ -3661,194 +3795,203 @@
       <c r="W58" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E59" s="3">
         <v>3700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4100</v>
       </c>
-      <c r="F59" s="3">
-        <v>3700</v>
-      </c>
       <c r="G59" s="3">
-        <v>5100</v>
+        <v>3500</v>
       </c>
       <c r="H59" s="3">
         <v>5100</v>
       </c>
       <c r="I59" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J59" s="3">
         <v>4100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E60" s="3">
         <v>5400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>5500</v>
+      </c>
+      <c r="H60" s="3">
+        <v>7300</v>
+      </c>
+      <c r="I60" s="3">
+        <v>7000</v>
+      </c>
+      <c r="J60" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K60" s="3">
+        <v>7800</v>
+      </c>
+      <c r="L60" s="3">
+        <v>6400</v>
+      </c>
+      <c r="M60" s="3">
         <v>5800</v>
       </c>
-      <c r="G60" s="3">
-        <v>7300</v>
-      </c>
-      <c r="H60" s="3">
-        <v>7000</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="N60" s="3">
         <v>6100</v>
       </c>
-      <c r="J60" s="3">
-        <v>7800</v>
-      </c>
-      <c r="K60" s="3">
-        <v>6400</v>
-      </c>
-      <c r="L60" s="3">
-        <v>5800</v>
-      </c>
-      <c r="M60" s="3">
-        <v>6100</v>
-      </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4200</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>4000</v>
       </c>
       <c r="R60" s="3">
         <v>4000</v>
       </c>
       <c r="S60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="T60" s="3">
         <v>3500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2700</v>
-      </c>
-      <c r="K61" s="3">
-        <v>2800</v>
       </c>
       <c r="L61" s="3">
         <v>2800</v>
       </c>
       <c r="M61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N61" s="3">
         <v>3400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1600</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>1100</v>
       </c>
       <c r="R61" s="3">
         <v>1100</v>
       </c>
       <c r="S61" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="T61" s="3">
         <v>1200</v>
       </c>
       <c r="U61" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="V61" s="3">
         <v>1300</v>
@@ -3856,25 +3999,28 @@
       <c r="W61" s="3">
         <v>1300</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>2600</v>
       </c>
       <c r="F62" s="3">
         <v>2600</v>
       </c>
       <c r="G62" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H62" s="3">
         <v>3000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>300</v>
       </c>
       <c r="I62" s="3">
         <v>300</v>
@@ -3883,7 +4029,7 @@
         <v>300</v>
       </c>
       <c r="K62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L62" s="3">
         <v>400</v>
@@ -3898,7 +4044,7 @@
         <v>400</v>
       </c>
       <c r="P62" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -3906,8 +4052,8 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>55</v>
+      <c r="S62" s="3">
+        <v>0</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>55</v>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E66" s="3">
         <v>8200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10700</v>
       </c>
-      <c r="F66" s="3">
-        <v>10600</v>
-      </c>
       <c r="G66" s="3">
+        <v>10400</v>
+      </c>
+      <c r="H66" s="3">
         <v>12800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5800</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>5100</v>
       </c>
       <c r="R66" s="3">
         <v>5100</v>
       </c>
       <c r="S66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="T66" s="3">
         <v>4700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-515200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-507300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-505000</v>
       </c>
-      <c r="F72" s="3">
-        <v>-498900</v>
-      </c>
       <c r="G72" s="3">
+        <v>-501600</v>
+      </c>
+      <c r="H72" s="3">
         <v>-493800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-489200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-481000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-471700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-462800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-453100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-446000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-440100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-434000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-429700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-425900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-422200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-418800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-415000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-410600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-406900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-404100</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>800</v>
       </c>
-      <c r="F76" s="3">
-        <v>6700</v>
-      </c>
       <c r="G76" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H76" s="3">
         <v>11200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>30200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>38500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>46800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>52300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>-2300</v>
+        <v>-4700</v>
       </c>
       <c r="E81" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-6100</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-5100</v>
       </c>
       <c r="G81" s="3">
         <v>-4600</v>
       </c>
       <c r="H81" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="I81" s="3">
         <v>-8200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,13 +5214,14 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
@@ -5079,10 +5278,13 @@
         <v>100</v>
       </c>
       <c r="W83" s="3">
+        <v>100</v>
+      </c>
+      <c r="X83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="M89" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="O89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="P89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-3400</v>
       </c>
-      <c r="E89" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-7600</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="R89" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="S89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="T89" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="U89" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="V89" s="3">
         <v>-3100</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-2300</v>
       </c>
       <c r="W89" s="3">
         <v>-2300</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>-2300</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,8 +5716,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5508,40 +5729,40 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -5556,13 +5777,16 @@
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,8 +5918,11 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5703,40 +5933,40 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3">
         <v>-100</v>
       </c>
       <c r="H94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-200</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-100</v>
       </c>
       <c r="P94" s="3">
         <v>-100</v>
       </c>
       <c r="Q94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -5751,13 +5981,16 @@
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,73 +6284,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-100</v>
       </c>
       <c r="F100" s="3">
         <v>-100</v>
       </c>
       <c r="G100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H100" s="3">
         <v>8800</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>48000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>11100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>6300</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>1900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>13600</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6171,69 +6420,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-3300</v>
+        <v>900</v>
       </c>
       <c r="E102" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-5800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>42700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>10000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AWH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AWH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>AWH</t>
   </si>
@@ -656,110 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -767,67 +774,73 @@
         <v>2200</v>
       </c>
       <c r="E8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G8" s="3">
         <v>4800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>2100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1400</v>
-      </c>
-      <c r="P8" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>700</v>
       </c>
       <c r="R8" s="3">
         <v>1200</v>
       </c>
       <c r="S8" s="3">
+        <v>700</v>
+      </c>
+      <c r="T8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="U8" s="3">
         <v>1300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1100</v>
-      </c>
-      <c r="V8" s="3">
-        <v>800</v>
-      </c>
-      <c r="W8" s="3">
-        <v>900</v>
       </c>
       <c r="X8" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>900</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -835,67 +848,73 @@
         <v>900</v>
       </c>
       <c r="E9" s="3">
+        <v>900</v>
+      </c>
+      <c r="F9" s="3">
+        <v>900</v>
+      </c>
+      <c r="G9" s="3">
         <v>2100</v>
       </c>
-      <c r="F9" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I9" s="3">
         <v>900</v>
-      </c>
-      <c r="H9" s="3">
-        <v>900</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1100</v>
       </c>
       <c r="J9" s="3">
         <v>900</v>
       </c>
       <c r="K9" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="L9" s="3">
         <v>900</v>
       </c>
       <c r="M9" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="N9" s="3">
         <v>900</v>
       </c>
       <c r="O9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P9" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q9" s="3">
         <v>1200</v>
-      </c>
-      <c r="P9" s="3">
-        <v>800</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>600</v>
       </c>
       <c r="R9" s="3">
         <v>800</v>
       </c>
       <c r="S9" s="3">
+        <v>600</v>
+      </c>
+      <c r="T9" s="3">
         <v>800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
+        <v>800</v>
+      </c>
+      <c r="V9" s="3">
         <v>900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -903,67 +922,73 @@
         <v>1300</v>
       </c>
       <c r="E10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G10" s="3">
         <v>2700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J10" s="3">
         <v>1200</v>
       </c>
-      <c r="G10" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>200</v>
-      </c>
-      <c r="P10" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>100</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
       </c>
       <c r="S10" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="T10" s="3">
         <v>400</v>
       </c>
       <c r="U10" s="3">
+        <v>500</v>
+      </c>
+      <c r="V10" s="3">
+        <v>400</v>
+      </c>
+      <c r="W10" s="3">
         <v>200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>100</v>
       </c>
-      <c r="X10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,76 +1013,84 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F12" s="3">
         <v>1000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>2000</v>
       </c>
-      <c r="F12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I12" s="3">
         <v>1000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>2200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1300</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1500</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1500</v>
       </c>
       <c r="M12" s="3">
         <v>1500</v>
       </c>
       <c r="N12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P12" s="3">
         <v>900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>400</v>
-      </c>
-      <c r="S12" s="3">
-        <v>200</v>
-      </c>
-      <c r="T12" s="3">
-        <v>300</v>
       </c>
       <c r="U12" s="3">
         <v>200</v>
       </c>
       <c r="V12" s="3">
+        <v>300</v>
+      </c>
+      <c r="W12" s="3">
         <v>200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y12" s="3">
         <v>100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1124,28 +1157,34 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>55</v>
+      <c r="E14" s="3">
+        <v>-1000</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="3">
-        <v>100</v>
+      <c r="G14" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>55</v>
+      <c r="I14" s="3">
+        <v>100</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>55</v>
@@ -1159,11 +1198,11 @@
       <c r="M14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1192,8 +1231,14 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1260,8 +1305,14 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1334,158 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F17" s="3">
         <v>6300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>15400</v>
       </c>
-      <c r="F17" s="3">
-        <v>8100</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I17" s="3">
         <v>7200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>10700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>10300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>11100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>10800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>11400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>9900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>7400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>7500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>5500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>5000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>4700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>5100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>5400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>4500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-10600</v>
       </c>
-      <c r="F18" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-5000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-8600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-8200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-9200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-8900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-9700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-8100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-5900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-6100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-3900</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-3400</v>
       </c>
       <c r="T18" s="3">
         <v>-3800</v>
       </c>
       <c r="U18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="W18" s="3">
         <v>-4300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-3700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-2800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1445,47 +1510,49 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>800</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>-100</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1493,14 +1560,14 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1513,76 +1580,88 @@
       <c r="X20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-8800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-6000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-9200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-3800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-3700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-3300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-3800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-4200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-3600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-2700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1649,76 +1728,88 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-4700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-8900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="O23" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-6100</v>
       </c>
-      <c r="G23" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-3800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-3700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-3400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-3800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-4300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-3700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-2800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1785,8 +1876,14 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1853,144 +1950,162 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-4700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-8900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="O26" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-6100</v>
       </c>
-      <c r="G26" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-3800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-3700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-3800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-4300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-3700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-2800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-4700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-8900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-6100</v>
       </c>
-      <c r="G27" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-3800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-3700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-3800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-4300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-3700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-2800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2057,8 +2172,14 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2125,8 +2246,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2193,8 +2320,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2261,47 +2394,53 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-800</v>
-      </c>
-      <c r="I32" s="3">
-        <v>100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>100</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
+        <v>100</v>
+      </c>
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2309,14 +2448,14 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -2329,76 +2468,88 @@
       <c r="X32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-4700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-8900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="O33" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-6100</v>
       </c>
-      <c r="G33" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-3800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-3700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-3800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-4300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-3700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-2800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2465,149 +2616,167 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-4700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-8900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="O35" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-6100</v>
       </c>
-      <c r="G35" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-3800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-3700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-3800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-4300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-3700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-2800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2632,8 +2801,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2658,76 +2829,84 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F41" s="3">
         <v>5100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>7500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>13300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>20600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>20500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>26900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>37200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>44900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>53000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>59400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>16600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>18800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>10900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>8100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>11700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>14600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>16200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>6200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>9400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2794,67 +2973,73 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="E43" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="F43" s="3">
         <v>1600</v>
       </c>
       <c r="G43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I43" s="3">
         <v>1200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1100</v>
-      </c>
-      <c r="J43" s="3">
-        <v>1100</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1000</v>
       </c>
       <c r="L43" s="3">
         <v>1100</v>
       </c>
       <c r="M43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N43" s="3">
         <v>1100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P43" s="3">
         <v>1000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1000</v>
-      </c>
-      <c r="U43" s="3">
-        <v>800</v>
-      </c>
-      <c r="V43" s="3">
-        <v>700</v>
       </c>
       <c r="W43" s="3">
         <v>800</v>
@@ -2862,16 +3047,22 @@
       <c r="X43" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F44" s="3">
         <v>300</v>
@@ -2883,46 +3074,46 @@
         <v>300</v>
       </c>
       <c r="I44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K44" s="3">
         <v>200</v>
       </c>
       <c r="L44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N44" s="3">
         <v>100</v>
       </c>
       <c r="O44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
         <v>100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>100</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
-      </c>
-      <c r="T44" s="3">
-        <v>0</v>
-      </c>
       <c r="U44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W44" s="3">
         <v>100</v>
@@ -2930,144 +3121,162 @@
       <c r="X44" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="3">
         <v>600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F46" s="3">
         <v>7600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>6900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>10500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>16300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>23000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>23000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>29800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>40000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>47200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>54900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>61400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>18600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>20300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>12700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>10000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>13400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>16100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>17600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>7600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>10800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -3134,8 +3343,14 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
@@ -3143,67 +3358,73 @@
         <v>800</v>
       </c>
       <c r="E48" s="3">
+        <v>700</v>
+      </c>
+      <c r="F48" s="3">
+        <v>800</v>
+      </c>
+      <c r="G48" s="3">
         <v>600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>700</v>
-      </c>
-      <c r="I48" s="3">
-        <v>800</v>
-      </c>
-      <c r="J48" s="3">
-        <v>800</v>
       </c>
       <c r="K48" s="3">
         <v>800</v>
       </c>
       <c r="L48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="M48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="N48" s="3">
         <v>900</v>
       </c>
       <c r="O48" s="3">
+        <v>900</v>
+      </c>
+      <c r="P48" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q48" s="3">
         <v>1000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>400</v>
-      </c>
-      <c r="R48" s="3">
-        <v>300</v>
       </c>
       <c r="S48" s="3">
         <v>400</v>
       </c>
       <c r="T48" s="3">
+        <v>300</v>
+      </c>
+      <c r="U48" s="3">
         <v>400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
+        <v>400</v>
+      </c>
+      <c r="W48" s="3">
         <v>500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
@@ -3270,8 +3491,14 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -3338,8 +3565,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -3406,8 +3639,14 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
@@ -3418,16 +3657,16 @@
         <v>300</v>
       </c>
       <c r="F52" s="3">
+        <v>300</v>
+      </c>
+      <c r="G52" s="3">
+        <v>300</v>
+      </c>
+      <c r="H52" s="3">
         <v>400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>300</v>
       </c>
       <c r="J52" s="3">
         <v>300</v>
@@ -3436,10 +3675,10 @@
         <v>300</v>
       </c>
       <c r="L52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -3457,10 +3696,10 @@
         <v>0</v>
       </c>
       <c r="S52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U52" s="3">
         <v>100</v>
@@ -3469,13 +3708,19 @@
         <v>100</v>
       </c>
       <c r="W52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -3542,76 +3787,88 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F54" s="3">
         <v>8700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>7700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>11500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>17400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>23900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>24000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>30900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>41100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>48000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>55800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>62300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>19600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>21300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>13100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>10400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>13800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>16500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>18200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>8300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>11400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -3636,8 +3893,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -3662,126 +3921,134 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
-      </c>
-      <c r="O57" s="3">
-        <v>1100</v>
-      </c>
-      <c r="P57" s="3">
-        <v>1300</v>
       </c>
       <c r="Q57" s="3">
         <v>1100</v>
       </c>
       <c r="R57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>800</v>
+      </c>
+      <c r="F58" s="3">
         <v>500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>600</v>
-      </c>
-      <c r="R58" s="3">
-        <v>200</v>
-      </c>
-      <c r="S58" s="3">
-        <v>200</v>
       </c>
       <c r="T58" s="3">
         <v>200</v>
@@ -3798,244 +4065,268 @@
       <c r="X58" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F59" s="3">
         <v>3300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>4100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>3500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>5100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>4100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>5100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>4000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>2200</v>
-      </c>
-      <c r="S59" s="3">
-        <v>2600</v>
-      </c>
-      <c r="T59" s="3">
-        <v>2500</v>
       </c>
       <c r="U59" s="3">
         <v>2600</v>
       </c>
       <c r="V59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="W59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="X59" s="3">
         <v>2000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F60" s="3">
         <v>5200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>5500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>7300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>6400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>5800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>6100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>6000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>4600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>4200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>4000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>4000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>3500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>3600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>3300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>3000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F61" s="3">
         <v>1200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>3400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1200</v>
-      </c>
-      <c r="V61" s="3">
-        <v>1300</v>
-      </c>
-      <c r="W61" s="3">
-        <v>1300</v>
       </c>
       <c r="X61" s="3">
         <v>1300</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F62" s="3">
         <v>2900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>2600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>3000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>300</v>
-      </c>
-      <c r="J62" s="3">
-        <v>300</v>
       </c>
       <c r="K62" s="3">
         <v>300</v>
       </c>
       <c r="L62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N62" s="3">
         <v>400</v>
@@ -4047,19 +4338,19 @@
         <v>400</v>
       </c>
       <c r="Q62" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="R62" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S62" s="3">
         <v>0</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>55</v>
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>55</v>
@@ -4070,8 +4361,14 @@
       <c r="X62" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4435,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -4206,8 +4509,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4583,88 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F66" s="3">
         <v>9300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>8200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>10700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>10400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>12800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>9900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>9100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>10900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>9500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>9000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>10000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>9900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>6700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>5800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>5100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>5100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>4700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>4800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>4600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>4300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4689,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4759,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4833,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4907,14 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4981,88 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-522900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-518300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-515200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-507300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-505000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-501600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-493800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-489200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-481000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-471700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-462800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-453100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-446000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-440100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-434000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-429700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-425900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-422200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-418800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-415000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-410600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-406900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-404100</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +5129,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5203,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5277,88 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F76" s="3">
         <v>-700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>7000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>11200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>14100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>21700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>30200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>38500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>46800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>52300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>9700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>14600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>7300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>5300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>8700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>11800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>13400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>3600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>7200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5425,167 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-4700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-8900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="M81" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="O81" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-6100</v>
       </c>
-      <c r="G81" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-3800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-3700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-3800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-4300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-3700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-2800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5610,10 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5224,10 +5621,10 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -5281,10 +5678,16 @@
         <v>100</v>
       </c>
       <c r="X83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5754,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5828,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5902,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5976,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +6050,88 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-3300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-9100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-5700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-7100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-7500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-6300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-10200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-7600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-8000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-6500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-5300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-4800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-3400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-3500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-3400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-3500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-3100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-2300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,8 +6156,10 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5732,13 +6173,13 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
@@ -5747,29 +6188,29 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -5780,13 +6221,19 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6300,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,8 +6374,14 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5936,13 +6395,13 @@
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
       </c>
       <c r="J94" s="3">
         <v>-100</v>
@@ -5951,29 +6410,29 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
@@ -5984,13 +6443,19 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6480,10 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6550,14 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6624,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6698,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,76 +6772,88 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F100" s="3">
         <v>4200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>8800</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>48000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>2800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>11100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>6300</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>1900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>13600</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6423,72 +6920,84 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F102" s="3">
         <v>900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-9100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-5800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-7200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-6400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-10300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-7700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-7900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-6400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>42700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-2200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>7900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>2800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-3600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-2900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>10000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-3200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-2400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-2400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AWH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AWH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>AWH</t>
   </si>
@@ -656,196 +656,203 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2200</v>
-      </c>
-      <c r="J8" s="3">
-        <v>2100</v>
       </c>
       <c r="K8" s="3">
         <v>2100</v>
       </c>
       <c r="L8" s="3">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="M8" s="3">
         <v>1900</v>
       </c>
       <c r="N8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O8" s="3">
         <v>1700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1200</v>
-      </c>
-      <c r="U8" s="3">
-        <v>1300</v>
       </c>
       <c r="V8" s="3">
         <v>1300</v>
       </c>
       <c r="W8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="X8" s="3">
         <v>1100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E9" s="3">
         <v>900</v>
@@ -854,141 +861,147 @@
         <v>900</v>
       </c>
       <c r="G9" s="3">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="H9" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I9" s="3">
         <v>2300</v>
-      </c>
-      <c r="I9" s="3">
-        <v>900</v>
       </c>
       <c r="J9" s="3">
         <v>900</v>
       </c>
       <c r="K9" s="3">
+        <v>900</v>
+      </c>
+      <c r="L9" s="3">
         <v>1100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>600</v>
-      </c>
-      <c r="T9" s="3">
-        <v>800</v>
       </c>
       <c r="U9" s="3">
         <v>800</v>
       </c>
       <c r="V9" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="W9" s="3">
         <v>900</v>
       </c>
       <c r="X9" s="3">
+        <v>900</v>
+      </c>
+      <c r="Y9" s="3">
         <v>700</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>800</v>
       </c>
       <c r="Z9" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E10" s="3">
         <v>1300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1300</v>
       </c>
-      <c r="G10" s="3">
-        <v>2700</v>
-      </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
         <v>1300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1200</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1000</v>
       </c>
       <c r="L10" s="3">
         <v>1000</v>
       </c>
       <c r="M10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N10" s="3">
         <v>1100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>200</v>
-      </c>
-      <c r="X10" s="3">
-        <v>100</v>
       </c>
       <c r="Y10" s="3">
         <v>100</v>
       </c>
       <c r="Z10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,40 +1028,41 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="3">
         <v>900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1300</v>
-      </c>
-      <c r="M12" s="3">
-        <v>1500</v>
       </c>
       <c r="N12" s="3">
         <v>1500</v>
@@ -1057,40 +1071,43 @@
         <v>1500</v>
       </c>
       <c r="P12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q12" s="3">
         <v>900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>600</v>
-      </c>
-      <c r="S12" s="3">
-        <v>400</v>
       </c>
       <c r="T12" s="3">
         <v>400</v>
       </c>
       <c r="U12" s="3">
+        <v>400</v>
+      </c>
+      <c r="V12" s="3">
         <v>200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>300</v>
-      </c>
-      <c r="W12" s="3">
-        <v>200</v>
       </c>
       <c r="X12" s="3">
         <v>200</v>
       </c>
       <c r="Y12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z12" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1163,31 +1180,34 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>55</v>
@@ -1204,8 +1224,8 @@
       <c r="O14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1237,8 +1257,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E17" s="3">
         <v>6900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6300</v>
       </c>
-      <c r="G17" s="3">
-        <v>15400</v>
-      </c>
       <c r="H17" s="3">
+        <v>14400</v>
+      </c>
+      <c r="I17" s="3">
         <v>8600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4100</v>
       </c>
-      <c r="G18" s="3">
-        <v>-10600</v>
-      </c>
       <c r="H18" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="I18" s="3">
         <v>-6300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-4300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1512,50 +1545,51 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
-        <v>1700</v>
-      </c>
       <c r="H20" s="3">
+        <v>700</v>
+      </c>
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>-100</v>
       </c>
       <c r="O20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1566,11 +1600,11 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1586,82 +1620,88 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-8800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-9200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-9600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-4200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1734,82 +1774,88 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1882,8 +1928,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2400,50 +2467,53 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
-        <v>-1700</v>
-      </c>
       <c r="H32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>100</v>
       </c>
       <c r="O32" s="3">
+        <v>100</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2454,11 +2524,11 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2474,82 +2544,88 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2831,82 +2917,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>20500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>26900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>37200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>44900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>53000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>59400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>16600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>18800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>14600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>16200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2979,19 +3069,22 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="E43" s="3">
         <v>1500</v>
       </c>
       <c r="F43" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="G43" s="3">
         <v>1600</v>
@@ -3000,61 +3093,64 @@
         <v>1600</v>
       </c>
       <c r="I43" s="3">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="J43" s="3">
         <v>1200</v>
       </c>
       <c r="K43" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="L43" s="3">
         <v>1100</v>
       </c>
       <c r="M43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N43" s="3">
         <v>1000</v>
-      </c>
-      <c r="N43" s="3">
-        <v>1100</v>
       </c>
       <c r="O43" s="3">
         <v>1100</v>
       </c>
       <c r="P43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q43" s="3">
         <v>1000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>900</v>
-      </c>
-      <c r="R43" s="3">
-        <v>800</v>
       </c>
       <c r="S43" s="3">
         <v>800</v>
       </c>
       <c r="T43" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="U43" s="3">
         <v>900</v>
       </c>
       <c r="V43" s="3">
+        <v>900</v>
+      </c>
+      <c r="W43" s="3">
         <v>1000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
@@ -3065,7 +3161,7 @@
         <v>200</v>
       </c>
       <c r="F44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G44" s="3">
         <v>300</v>
@@ -3080,7 +3176,7 @@
         <v>300</v>
       </c>
       <c r="K44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L44" s="3">
         <v>200</v>
@@ -3089,7 +3185,7 @@
         <v>200</v>
       </c>
       <c r="N44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O44" s="3">
         <v>100</v>
@@ -3098,25 +3194,25 @@
         <v>100</v>
       </c>
       <c r="Q44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
       <c r="S44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T44" s="3">
         <v>100</v>
       </c>
       <c r="U44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
       </c>
       <c r="W44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X44" s="3">
         <v>100</v>
@@ -3127,156 +3223,165 @@
       <c r="Z44" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3">
         <v>900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1600</v>
       </c>
       <c r="M45" s="3">
         <v>1600</v>
       </c>
       <c r="N45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O45" s="3">
         <v>1100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>900</v>
-      </c>
-      <c r="T45" s="3">
-        <v>800</v>
       </c>
       <c r="U45" s="3">
         <v>800</v>
       </c>
       <c r="V45" s="3">
+        <v>800</v>
+      </c>
+      <c r="W45" s="3">
         <v>400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>500</v>
-      </c>
-      <c r="X45" s="3">
-        <v>600</v>
       </c>
       <c r="Y45" s="3">
         <v>600</v>
       </c>
       <c r="Z45" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA45" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E46" s="3">
         <v>6100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16300</v>
-      </c>
-      <c r="J46" s="3">
-        <v>23000</v>
       </c>
       <c r="K46" s="3">
         <v>23000</v>
       </c>
       <c r="L46" s="3">
+        <v>23000</v>
+      </c>
+      <c r="M46" s="3">
         <v>29800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>40000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>47200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>54900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>61400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>18600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>20300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>13400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>16100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>17600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -3349,34 +3454,37 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>700</v>
+      </c>
+      <c r="E48" s="3">
         <v>800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>800</v>
-      </c>
-      <c r="G48" s="3">
-        <v>600</v>
       </c>
       <c r="H48" s="3">
         <v>600</v>
       </c>
       <c r="I48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="J48" s="3">
         <v>700</v>
       </c>
       <c r="K48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="L48" s="3">
         <v>800</v>
@@ -3385,7 +3493,7 @@
         <v>800</v>
       </c>
       <c r="N48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="O48" s="3">
         <v>900</v>
@@ -3394,37 +3502,40 @@
         <v>900</v>
       </c>
       <c r="Q48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="R48" s="3">
         <v>1000</v>
       </c>
       <c r="S48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T48" s="3">
         <v>400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>300</v>
-      </c>
-      <c r="U48" s="3">
-        <v>400</v>
       </c>
       <c r="V48" s="3">
         <v>400</v>
       </c>
       <c r="W48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="X48" s="3">
         <v>500</v>
       </c>
       <c r="Y48" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z48" s="3">
         <v>600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
@@ -3497,8 +3608,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -3645,13 +3762,16 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
         <v>300</v>
@@ -3663,13 +3783,13 @@
         <v>300</v>
       </c>
       <c r="H52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I52" s="3">
         <v>400</v>
       </c>
       <c r="J52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K52" s="3">
         <v>300</v>
@@ -3681,7 +3801,7 @@
         <v>300</v>
       </c>
       <c r="N52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -3702,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V52" s="3">
         <v>100</v>
@@ -3714,13 +3834,16 @@
         <v>100</v>
       </c>
       <c r="Y52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -3793,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E54" s="3">
         <v>7200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>30900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>41100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>48000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>55800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>62300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>19600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>21300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>18200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>11400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -3923,135 +4053,139 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>900</v>
       </c>
       <c r="I57" s="3">
         <v>900</v>
       </c>
       <c r="J57" s="3">
+        <v>900</v>
+      </c>
+      <c r="K57" s="3">
         <v>1900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
         <v>700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>600</v>
-      </c>
-      <c r="T58" s="3">
-        <v>200</v>
       </c>
       <c r="U58" s="3">
         <v>200</v>
@@ -4071,8 +4205,11 @@
       <c r="Z58" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
@@ -4083,144 +4220,150 @@
         <v>3000</v>
       </c>
       <c r="F59" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G59" s="3">
         <v>3300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3500</v>
-      </c>
-      <c r="J59" s="3">
-        <v>5100</v>
       </c>
       <c r="K59" s="3">
         <v>5100</v>
       </c>
       <c r="L59" s="3">
+        <v>5100</v>
+      </c>
+      <c r="M59" s="3">
         <v>4100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E60" s="3">
         <v>5300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4200</v>
-      </c>
-      <c r="T60" s="3">
-        <v>4000</v>
       </c>
       <c r="U60" s="3">
         <v>4000</v>
       </c>
       <c r="V60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W60" s="3">
         <v>3500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
@@ -4228,64 +4371,64 @@
         <v>1300</v>
       </c>
       <c r="E61" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F61" s="3">
         <v>1400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2700</v>
-      </c>
-      <c r="N61" s="3">
-        <v>2800</v>
       </c>
       <c r="O61" s="3">
         <v>2800</v>
       </c>
       <c r="P61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Q61" s="3">
         <v>3400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1600</v>
-      </c>
-      <c r="T61" s="3">
-        <v>1100</v>
       </c>
       <c r="U61" s="3">
         <v>1100</v>
       </c>
       <c r="V61" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="W61" s="3">
         <v>1200</v>
       </c>
       <c r="X61" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="Y61" s="3">
         <v>1300</v>
@@ -4293,34 +4436,37 @@
       <c r="Z61" s="3">
         <v>1300</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>2600</v>
       </c>
       <c r="I62" s="3">
         <v>2600</v>
       </c>
       <c r="J62" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K62" s="3">
         <v>3000</v>
-      </c>
-      <c r="K62" s="3">
-        <v>300</v>
       </c>
       <c r="L62" s="3">
         <v>300</v>
@@ -4329,7 +4475,7 @@
         <v>300</v>
       </c>
       <c r="N62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O62" s="3">
         <v>400</v>
@@ -4344,7 +4490,7 @@
         <v>400</v>
       </c>
       <c r="S62" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
@@ -4352,8 +4498,8 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>55</v>
+      <c r="V62" s="3">
+        <v>0</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>55</v>
@@ -4367,8 +4513,11 @@
       <c r="Z62" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E66" s="3">
         <v>8500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5800</v>
-      </c>
-      <c r="T66" s="3">
-        <v>5100</v>
       </c>
       <c r="U66" s="3">
         <v>5100</v>
       </c>
       <c r="V66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="W66" s="3">
         <v>4700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-526500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-522900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-518300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-515200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-507300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-505000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-501600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-493800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-489200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-481000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-471700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-462800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-453100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-446000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-440100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-434000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-429700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-425900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-422200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-418800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-415000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-410600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-406900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-404100</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-2400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>30200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>38500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>46800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>52300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5627,7 +5826,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -5684,10 +5883,13 @@
         <v>100</v>
       </c>
       <c r="Z83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3100</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-2300</v>
       </c>
       <c r="Z89" s="3">
         <v>-2300</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>-2300</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,8 +6378,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6179,40 +6400,40 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-200</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-100</v>
       </c>
       <c r="S91" s="3">
         <v>-100</v>
       </c>
       <c r="T91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -6227,13 +6448,16 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,8 +6607,11 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6401,40 +6631,40 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3">
         <v>-100</v>
       </c>
       <c r="K94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-200</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-100</v>
       </c>
       <c r="S94" s="3">
         <v>-100</v>
       </c>
       <c r="T94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -6449,13 +6679,16 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,82 +7021,88 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E100" s="3">
         <v>5300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>8800</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>48000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>11100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>6300</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>1900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>13600</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6926,78 +7175,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E102" s="3">
         <v>800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>42700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>7900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>10000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AWH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AWH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>AWH</t>
   </si>
@@ -656,206 +656,213 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2200</v>
       </c>
-      <c r="H8" s="3">
-        <v>4800</v>
-      </c>
       <c r="I8" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J8" s="3">
         <v>2300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2200</v>
-      </c>
-      <c r="K8" s="3">
-        <v>2100</v>
       </c>
       <c r="L8" s="3">
         <v>2100</v>
       </c>
       <c r="M8" s="3">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="N8" s="3">
         <v>1900</v>
       </c>
       <c r="O8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P8" s="3">
         <v>1700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1200</v>
-      </c>
-      <c r="V8" s="3">
-        <v>1300</v>
       </c>
       <c r="W8" s="3">
         <v>1300</v>
       </c>
       <c r="X8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Y8" s="3">
         <v>1100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1000</v>
-      </c>
-      <c r="E9" s="3">
-        <v>900</v>
       </c>
       <c r="F9" s="3">
         <v>900</v>
@@ -864,67 +871,70 @@
         <v>900</v>
       </c>
       <c r="H9" s="3">
-        <v>4100</v>
+        <v>900</v>
       </c>
       <c r="I9" s="3">
-        <v>2300</v>
+        <v>900</v>
       </c>
       <c r="J9" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="K9" s="3">
         <v>900</v>
       </c>
       <c r="L9" s="3">
+        <v>900</v>
+      </c>
+      <c r="M9" s="3">
         <v>1100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>600</v>
-      </c>
-      <c r="U9" s="3">
-        <v>800</v>
       </c>
       <c r="V9" s="3">
         <v>800</v>
       </c>
       <c r="W9" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="X9" s="3">
         <v>900</v>
       </c>
       <c r="Y9" s="3">
+        <v>900</v>
+      </c>
+      <c r="Z9" s="3">
         <v>700</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>800</v>
       </c>
       <c r="AA9" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -932,76 +942,79 @@
         <v>1400</v>
       </c>
       <c r="E10" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="F10" s="3">
         <v>1200</v>
       </c>
       <c r="G10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H10" s="3">
         <v>1300</v>
       </c>
-      <c r="H10" s="3">
-        <v>700</v>
-      </c>
       <c r="I10" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="J10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K10" s="3">
         <v>1300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1200</v>
-      </c>
-      <c r="L10" s="3">
-        <v>1000</v>
       </c>
       <c r="M10" s="3">
         <v>1000</v>
       </c>
       <c r="N10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O10" s="3">
         <v>1100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>200</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>100</v>
       </c>
       <c r="Z10" s="3">
         <v>100</v>
       </c>
       <c r="AA10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1029,43 +1042,44 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E12" s="3">
         <v>900</v>
       </c>
       <c r="F12" s="3">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="G12" s="3">
         <v>1000</v>
       </c>
       <c r="H12" s="3">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I12" s="3">
+        <v>700</v>
+      </c>
+      <c r="J12" s="3">
         <v>1300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1300</v>
-      </c>
-      <c r="N12" s="3">
-        <v>1500</v>
       </c>
       <c r="O12" s="3">
         <v>1500</v>
@@ -1074,40 +1088,43 @@
         <v>1500</v>
       </c>
       <c r="Q12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R12" s="3">
         <v>900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>600</v>
-      </c>
-      <c r="T12" s="3">
-        <v>400</v>
       </c>
       <c r="U12" s="3">
         <v>400</v>
       </c>
       <c r="V12" s="3">
+        <v>400</v>
+      </c>
+      <c r="W12" s="3">
         <v>200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>300</v>
-      </c>
-      <c r="X12" s="3">
-        <v>200</v>
       </c>
       <c r="Y12" s="3">
         <v>200</v>
       </c>
       <c r="Z12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA12" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1183,34 +1200,37 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="3">
         <v>-1000</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H14" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>55</v>
@@ -1227,8 +1247,8 @@
       <c r="P14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1260,8 +1280,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1281,10 +1304,10 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6900</v>
-      </c>
-      <c r="F17" s="3">
-        <v>5300</v>
       </c>
       <c r="G17" s="3">
         <v>6300</v>
       </c>
       <c r="H17" s="3">
-        <v>14400</v>
+        <v>6300</v>
       </c>
       <c r="I17" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J17" s="3">
         <v>8600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4700</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-3200</v>
       </c>
       <c r="G18" s="3">
         <v>-4100</v>
       </c>
       <c r="H18" s="3">
-        <v>-9600</v>
+        <v>-4100</v>
       </c>
       <c r="I18" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="J18" s="3">
         <v>-6300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1546,53 +1579,54 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>900</v>
+        <v>-200</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>-600</v>
+        <v>-400</v>
       </c>
       <c r="H20" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="I20" s="3">
-        <v>-300</v>
+        <v>-1000</v>
       </c>
       <c r="J20" s="3">
+        <v>300</v>
+      </c>
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>-100</v>
       </c>
       <c r="P20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>1000</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1603,11 +1637,11 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1623,8 +1657,11 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1632,76 +1669,79 @@
         <v>-3500</v>
       </c>
       <c r="E21" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4600</v>
       </c>
-      <c r="F21" s="3">
-        <v>-3100</v>
-      </c>
       <c r="G21" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="H21" s="3">
         <v>-4700</v>
       </c>
-      <c r="H21" s="3">
-        <v>-8800</v>
-      </c>
       <c r="I21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="J21" s="3">
         <v>-6500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-9200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-9600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1714,17 +1754,17 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1777,8 +1817,11 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
@@ -1786,99 +1829,102 @@
         <v>-3500</v>
       </c>
       <c r="E23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-4600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4700</v>
       </c>
-      <c r="H23" s="3">
-        <v>-8900</v>
-      </c>
       <c r="I23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J23" s="3">
         <v>-6600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1931,8 +1977,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2008,8 +2057,11 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
@@ -2017,76 +2069,79 @@
         <v>-3500</v>
       </c>
       <c r="E26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-4600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4700</v>
       </c>
-      <c r="H26" s="3">
-        <v>-8900</v>
-      </c>
       <c r="I26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J26" s="3">
         <v>-6600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
@@ -2094,76 +2149,79 @@
         <v>-3500</v>
       </c>
       <c r="E27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-4600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4700</v>
       </c>
-      <c r="H27" s="3">
-        <v>-8900</v>
-      </c>
       <c r="I27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J27" s="3">
         <v>-6600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2470,53 +2537,56 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-900</v>
+        <v>200</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="H32" s="3">
-        <v>-700</v>
+        <v>-600</v>
       </c>
       <c r="I32" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="J32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>100</v>
       </c>
       <c r="P32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2527,11 +2597,11 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -2547,8 +2617,11 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
@@ -2556,76 +2629,79 @@
         <v>-3500</v>
       </c>
       <c r="E33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-4600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4700</v>
       </c>
-      <c r="H33" s="3">
-        <v>-8900</v>
-      </c>
       <c r="I33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J33" s="3">
         <v>-6600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2701,8 +2777,11 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
@@ -2710,158 +2789,164 @@
         <v>-3500</v>
       </c>
       <c r="E35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-4600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4700</v>
       </c>
-      <c r="H35" s="3">
-        <v>-8900</v>
-      </c>
       <c r="I35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J35" s="3">
         <v>-6600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2918,85 +3004,89 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>20600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>20500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>37200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>44900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>53000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>59400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>16600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>18800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>14600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>16200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -3072,22 +3162,25 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1400</v>
-      </c>
-      <c r="E43" s="3">
-        <v>1500</v>
       </c>
       <c r="F43" s="3">
         <v>1500</v>
       </c>
       <c r="G43" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="H43" s="3">
         <v>1600</v>
@@ -3096,66 +3189,69 @@
         <v>1600</v>
       </c>
       <c r="J43" s="3">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="K43" s="3">
         <v>1200</v>
       </c>
       <c r="L43" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="M43" s="3">
         <v>1100</v>
       </c>
       <c r="N43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O43" s="3">
         <v>1000</v>
-      </c>
-      <c r="O43" s="3">
-        <v>1100</v>
       </c>
       <c r="P43" s="3">
         <v>1100</v>
       </c>
       <c r="Q43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R43" s="3">
         <v>1000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>900</v>
-      </c>
-      <c r="S43" s="3">
-        <v>800</v>
       </c>
       <c r="T43" s="3">
         <v>800</v>
       </c>
       <c r="U43" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="V43" s="3">
         <v>900</v>
       </c>
       <c r="W43" s="3">
+        <v>900</v>
+      </c>
+      <c r="X43" s="3">
         <v>1000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E44" s="3">
         <v>200</v>
@@ -3164,7 +3260,7 @@
         <v>200</v>
       </c>
       <c r="G44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H44" s="3">
         <v>300</v>
@@ -3179,7 +3275,7 @@
         <v>300</v>
       </c>
       <c r="L44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M44" s="3">
         <v>200</v>
@@ -3188,7 +3284,7 @@
         <v>200</v>
       </c>
       <c r="O44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P44" s="3">
         <v>100</v>
@@ -3197,25 +3293,25 @@
         <v>100</v>
       </c>
       <c r="R44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
       </c>
       <c r="T44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U44" s="3">
         <v>100</v>
       </c>
       <c r="V44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
       </c>
       <c r="X44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y44" s="3">
         <v>100</v>
@@ -3226,185 +3322,194 @@
       <c r="AA44" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
+        <v>300</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H45" s="3">
+        <v>500</v>
+      </c>
+      <c r="I45" s="3">
+        <v>400</v>
+      </c>
+      <c r="J45" s="3">
+        <v>300</v>
+      </c>
+      <c r="K45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="F45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="K45" s="3">
-        <v>900</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1200</v>
-      </c>
-      <c r="M45" s="3">
-        <v>1600</v>
       </c>
       <c r="N45" s="3">
         <v>1600</v>
       </c>
       <c r="O45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P45" s="3">
         <v>1100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>900</v>
-      </c>
-      <c r="U45" s="3">
-        <v>800</v>
       </c>
       <c r="V45" s="3">
         <v>800</v>
       </c>
       <c r="W45" s="3">
+        <v>800</v>
+      </c>
+      <c r="X45" s="3">
         <v>400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>500</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>600</v>
       </c>
       <c r="Z45" s="3">
         <v>600</v>
       </c>
       <c r="AA45" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB45" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E46" s="3">
         <v>3300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16300</v>
-      </c>
-      <c r="K46" s="3">
-        <v>23000</v>
       </c>
       <c r="L46" s="3">
         <v>23000</v>
       </c>
       <c r="M46" s="3">
+        <v>23000</v>
+      </c>
+      <c r="N46" s="3">
         <v>29800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>40000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>47200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>54900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>61400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>18600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>20300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>13400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>16100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3457,37 +3562,40 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>600</v>
+      </c>
+      <c r="E48" s="3">
         <v>700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>800</v>
-      </c>
-      <c r="H48" s="3">
-        <v>600</v>
       </c>
       <c r="I48" s="3">
         <v>600</v>
       </c>
       <c r="J48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="K48" s="3">
         <v>700</v>
       </c>
       <c r="L48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="M48" s="3">
         <v>800</v>
@@ -3496,7 +3604,7 @@
         <v>800</v>
       </c>
       <c r="O48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="P48" s="3">
         <v>900</v>
@@ -3505,37 +3613,40 @@
         <v>900</v>
       </c>
       <c r="R48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="S48" s="3">
         <v>1000</v>
       </c>
       <c r="T48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U48" s="3">
         <v>400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>300</v>
-      </c>
-      <c r="V48" s="3">
-        <v>400</v>
       </c>
       <c r="W48" s="3">
         <v>400</v>
       </c>
       <c r="X48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Y48" s="3">
         <v>500</v>
       </c>
       <c r="Z48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA48" s="3">
         <v>600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -3765,8 +3882,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
@@ -3774,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
         <v>300</v>
@@ -3786,13 +3906,13 @@
         <v>300</v>
       </c>
       <c r="I52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J52" s="3">
         <v>400</v>
       </c>
       <c r="K52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L52" s="3">
         <v>300</v>
@@ -3804,7 +3924,7 @@
         <v>300</v>
       </c>
       <c r="O52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -3825,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W52" s="3">
         <v>100</v>
@@ -3837,13 +3957,16 @@
         <v>100</v>
       </c>
       <c r="Z52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -3919,85 +4042,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E54" s="3">
         <v>4000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>30900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>41100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>48000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>55800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>62300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>19600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>21300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>18200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4054,141 +4184,145 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>900</v>
       </c>
       <c r="J57" s="3">
         <v>900</v>
       </c>
       <c r="K57" s="3">
+        <v>900</v>
+      </c>
+      <c r="L57" s="3">
         <v>1900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E58" s="3">
         <v>700</v>
       </c>
       <c r="F58" s="3">
+        <v>900</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H58" s="3">
+        <v>700</v>
+      </c>
+      <c r="I58" s="3">
         <v>800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="J58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L58" s="3">
+        <v>300</v>
+      </c>
+      <c r="M58" s="3">
         <v>500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="N58" s="3">
+        <v>700</v>
+      </c>
+      <c r="O58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P58" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>400</v>
+      </c>
+      <c r="R58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T58" s="3">
+        <v>500</v>
+      </c>
+      <c r="U58" s="3">
         <v>600</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>1200</v>
-      </c>
-      <c r="K58" s="3">
-        <v>300</v>
-      </c>
-      <c r="L58" s="3">
-        <v>500</v>
-      </c>
-      <c r="M58" s="3">
-        <v>700</v>
-      </c>
-      <c r="N58" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>200</v>
-      </c>
-      <c r="P58" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>1100</v>
-      </c>
-      <c r="R58" s="3">
-        <v>1300</v>
-      </c>
-      <c r="S58" s="3">
-        <v>500</v>
-      </c>
-      <c r="T58" s="3">
-        <v>600</v>
-      </c>
-      <c r="U58" s="3">
-        <v>200</v>
       </c>
       <c r="V58" s="3">
         <v>200</v>
@@ -4208,85 +4342,91 @@
       <c r="AA58" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D59" s="3">
-        <v>3000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>3000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>3000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>3300</v>
-      </c>
-      <c r="H59" s="3">
-        <v>3700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>4100</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K59" s="3">
         <v>3500</v>
-      </c>
-      <c r="K59" s="3">
-        <v>5100</v>
       </c>
       <c r="L59" s="3">
         <v>5100</v>
       </c>
       <c r="M59" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N59" s="3">
         <v>4100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
@@ -4294,144 +4434,147 @@
         <v>5500</v>
       </c>
       <c r="E60" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F60" s="3">
         <v>5300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4200</v>
-      </c>
-      <c r="U60" s="3">
-        <v>4000</v>
       </c>
       <c r="V60" s="3">
         <v>4000</v>
       </c>
       <c r="W60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="X60" s="3">
         <v>3500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>1300</v>
+        <v>1700</v>
       </c>
       <c r="E61" s="3">
-        <v>1300</v>
+        <v>1700</v>
       </c>
       <c r="F61" s="3">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="G61" s="3">
-        <v>1200</v>
+        <v>1900</v>
       </c>
       <c r="H61" s="3">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="I61" s="3">
-        <v>2200</v>
+        <v>1600</v>
       </c>
       <c r="J61" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K61" s="3">
         <v>2300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2700</v>
-      </c>
-      <c r="O61" s="3">
-        <v>2800</v>
       </c>
       <c r="P61" s="3">
         <v>2800</v>
       </c>
       <c r="Q61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="R61" s="3">
         <v>3400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1600</v>
-      </c>
-      <c r="U61" s="3">
-        <v>1100</v>
       </c>
       <c r="V61" s="3">
         <v>1100</v>
       </c>
       <c r="W61" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="X61" s="3">
         <v>1200</v>
       </c>
       <c r="Y61" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="Z61" s="3">
         <v>1300</v>
@@ -4439,37 +4582,40 @@
       <c r="AA61" s="3">
         <v>1300</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="E62" s="3">
-        <v>1900</v>
+        <v>500</v>
       </c>
       <c r="F62" s="3">
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="G62" s="3">
-        <v>2900</v>
+        <v>1700</v>
       </c>
       <c r="H62" s="3">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="I62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K62" s="3">
         <v>2600</v>
       </c>
-      <c r="J62" s="3">
-        <v>2600</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3000</v>
-      </c>
-      <c r="L62" s="3">
-        <v>300</v>
       </c>
       <c r="M62" s="3">
         <v>300</v>
@@ -4478,7 +4624,7 @@
         <v>300</v>
       </c>
       <c r="O62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="P62" s="3">
         <v>400</v>
@@ -4493,7 +4639,7 @@
         <v>400</v>
       </c>
       <c r="T62" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -4501,8 +4647,8 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>55</v>
+      <c r="W62" s="3">
+        <v>0</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>55</v>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,85 +4902,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E66" s="3">
         <v>7700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5800</v>
-      </c>
-      <c r="U66" s="3">
-        <v>5100</v>
       </c>
       <c r="V66" s="3">
         <v>5100</v>
       </c>
       <c r="W66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="X66" s="3">
         <v>4700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,85 +5332,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-530000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-526500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-522900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-518300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-515200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-507300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-505000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-501600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-493800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-489200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-481000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-471700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-462800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-453100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-446000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-440100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-434000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-429700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-425900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-422200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-418800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-415000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-410600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-406900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-404100</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-3700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-2400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>30200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>38500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>46800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>52300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,90 +5812,96 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
@@ -5714,76 +5909,79 @@
         <v>-3500</v>
       </c>
       <c r="E81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-4600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4700</v>
       </c>
-      <c r="H81" s="3">
-        <v>-8900</v>
-      </c>
       <c r="I81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J81" s="3">
         <v>-6600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,8 +6009,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5820,13 +6019,13 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -5886,10 +6085,13 @@
         <v>100</v>
       </c>
       <c r="AA83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3300</v>
       </c>
-      <c r="H89" s="3">
-        <v>-9100</v>
-      </c>
       <c r="I89" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="J89" s="3">
         <v>-5700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3100</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-2300</v>
       </c>
       <c r="AA89" s="3">
         <v>-2300</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>-2300</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,8 +6599,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6403,40 +6624,40 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-200</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-100</v>
       </c>
       <c r="T91" s="3">
         <v>-100</v>
       </c>
       <c r="U91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -6451,13 +6672,16 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,8 +6837,11 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6634,40 +6864,40 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K94" s="3">
         <v>-100</v>
       </c>
       <c r="L94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-200</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-100</v>
       </c>
       <c r="T94" s="3">
         <v>-100</v>
       </c>
       <c r="U94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -6682,13 +6912,16 @@
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,31 +6949,32 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,108 +7267,114 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E100" s="3">
         <v>1000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8800</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>48000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>11100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>6300</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>1900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>13600</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7178,81 +7427,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>900</v>
       </c>
-      <c r="H102" s="3">
-        <v>-9100</v>
-      </c>
       <c r="I102" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="J102" s="3">
         <v>-5800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>42700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>7900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>10000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2400</v>
       </c>
     </row>
